--- a/Result/checksun/數位雲端.xlsx
+++ b/Result/checksun/數位雲端.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20329,7 +20529,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20617,7 +20821,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20905,7 +21113,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -21193,7 +21405,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21481,7 +21697,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21769,7 +21989,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -22057,7 +22281,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22345,7 +22573,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22633,7 +22865,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22921,7 +23157,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26669,7 +26909,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26957,7 +27201,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -27245,7 +27493,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27533,7 +27785,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27821,7 +28077,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -28109,7 +28369,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28397,7 +28661,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28685,7 +28953,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28973,7 +29245,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -29261,7 +29537,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr"/>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -33009,7 +33289,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -33297,7 +33581,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -33585,7 +33873,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -33873,7 +34165,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -34161,7 +34457,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -34449,7 +34749,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -34737,7 +35041,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -35025,7 +35333,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -35313,7 +35625,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -35601,7 +35917,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr"/>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -36181,7 +36501,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -36469,7 +36793,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -36757,7 +37085,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -37045,7 +37377,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -37333,7 +37669,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -37621,7 +37961,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -37909,7 +38253,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -38197,7 +38545,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -38485,7 +38837,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -38773,7 +39129,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -39353,7 +39713,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -39641,7 +40005,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -39929,7 +40297,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -40217,7 +40589,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -40505,7 +40881,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -40793,7 +41173,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -41081,7 +41465,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -41369,7 +41757,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -41657,7 +42049,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -41945,7 +42341,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -42525,7 +42925,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -42813,7 +43217,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -43101,7 +43509,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -43389,7 +43801,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -43677,7 +44093,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -43965,7 +44385,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -44253,7 +44677,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -44541,7 +44969,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -44829,7 +45261,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -45117,7 +45553,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -45697,7 +46137,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -45985,7 +46429,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -46273,7 +46721,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -46561,7 +47013,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -46849,7 +47305,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -47137,7 +47597,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -47425,7 +47889,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -47713,7 +48181,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -48001,7 +48473,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -48289,7 +48765,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -48869,7 +49349,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -49157,7 +49641,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -49445,7 +49933,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -49733,7 +50225,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -50021,7 +50517,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -50309,7 +50809,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -50597,7 +51101,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -50885,7 +51393,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -51173,7 +51685,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -51461,7 +51977,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -52041,7 +52561,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -52329,7 +52853,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -52617,7 +53145,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -52905,7 +53437,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -53193,7 +53729,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -53481,7 +54021,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -53769,7 +54313,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -54057,7 +54605,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -54345,7 +54897,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -54633,7 +55189,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -55213,7 +55773,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -55501,7 +56065,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -55789,7 +56357,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -56077,7 +56649,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -56365,7 +56941,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -56653,7 +57233,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -56941,7 +57525,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -57229,7 +57817,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -57517,7 +58109,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -57805,7 +58401,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -58385,7 +58985,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -58673,7 +59277,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -58961,7 +59569,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -59249,7 +59861,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -59537,7 +60153,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -59825,7 +60445,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -60113,7 +60737,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -60401,7 +61029,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -60689,7 +61321,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -60977,7 +61613,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -61557,7 +62197,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -61845,7 +62489,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -62133,7 +62781,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -62421,7 +63073,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -62709,7 +63365,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -62997,7 +63657,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -63285,7 +63949,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -63573,7 +64241,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -63861,7 +64533,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -64149,7 +64825,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr"/>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -64729,7 +65409,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -65017,7 +65701,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -65305,7 +65993,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -65593,7 +66285,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -65881,7 +66577,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -66169,7 +66869,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -66457,7 +67161,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -66745,7 +67453,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -67033,7 +67745,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -67321,7 +68037,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -67901,7 +68621,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -68189,7 +68913,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -68477,7 +69205,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -68765,7 +69497,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -69053,7 +69789,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -69341,7 +70081,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -69629,7 +70373,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr"/>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -69917,7 +70665,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -70205,7 +70957,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr"/>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -70493,7 +71249,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr"/>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -71073,7 +71833,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr"/>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -71361,7 +72125,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr"/>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -71649,7 +72417,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr"/>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -71937,7 +72709,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr"/>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -72225,7 +73001,11 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr"/>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -72513,7 +73293,11 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr"/>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -72801,7 +73585,11 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr"/>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -73089,7 +73877,11 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -73377,7 +74169,11 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -73665,7 +74461,11 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr"/>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -74245,7 +75045,11 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr"/>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -74533,7 +75337,11 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr"/>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -74821,7 +75629,11 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr"/>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -75109,7 +75921,11 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr"/>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -75397,7 +76213,11 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr"/>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -75685,7 +76505,11 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr"/>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -75973,7 +76797,11 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr"/>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -76261,7 +77089,11 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -76549,7 +77381,11 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -76837,7 +77673,11 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -77417,7 +78257,11 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr"/>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -77705,7 +78549,11 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr"/>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -77993,7 +78841,11 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr"/>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -78281,7 +79133,11 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr"/>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -78569,7 +79425,11 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr"/>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -78857,7 +79717,11 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr"/>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -79145,7 +80009,11 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr"/>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -79433,7 +80301,11 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr"/>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -79721,7 +80593,11 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr"/>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -80009,7 +80885,11 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr"/>
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -80589,7 +81469,11 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr"/>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -80877,7 +81761,11 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr"/>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -81165,7 +82053,11 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr"/>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -81453,7 +82345,11 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr"/>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -81741,7 +82637,11 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr"/>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -82029,7 +82929,11 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr"/>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -82317,7 +83221,11 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr"/>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -82605,7 +83513,11 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr"/>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -82893,7 +83805,11 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr"/>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -83181,7 +84097,11 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr"/>
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -83761,7 +84681,11 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr"/>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -84049,7 +84973,11 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr"/>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -84337,7 +85265,11 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr"/>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -84625,7 +85557,11 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr"/>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -84913,7 +85849,11 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr"/>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -85201,7 +86141,11 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr"/>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -85489,7 +86433,11 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -85777,7 +86725,11 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr"/>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -86065,7 +87017,11 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr"/>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -86353,7 +87309,11 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr"/>
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -86933,7 +87893,11 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr"/>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -87221,7 +88185,11 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr"/>
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -87509,7 +88477,11 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr"/>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -87797,7 +88769,11 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr"/>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -88085,7 +89061,11 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr"/>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -88373,7 +89353,11 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr"/>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -88661,7 +89645,11 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr"/>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -88949,7 +89937,11 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr"/>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -89237,7 +90229,11 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr"/>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -89525,7 +90521,11 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr"/>
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -90105,7 +91105,11 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr"/>
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -90393,7 +91397,11 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr"/>
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -90681,7 +91689,11 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr"/>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -90969,7 +91981,11 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr"/>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -91257,7 +92273,11 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr"/>
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -91545,7 +92565,11 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr"/>
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -91833,7 +92857,11 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr"/>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -92121,7 +93149,11 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr"/>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -92409,7 +93441,11 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -92697,7 +93733,11 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr"/>
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>2025-08-25</t>
